--- a/Team-Data/2007-08/1-24-2007-08.xlsx
+++ b/Team-Data/2007-08/1-24-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -793,7 +860,7 @@
         <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -802,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>11.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -975,13 +1042,13 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>4</v>
@@ -1142,7 +1209,7 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
@@ -1157,7 +1224,7 @@
         <v>17</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>13</v>
@@ -1175,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
@@ -1309,10 +1376,10 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN5" t="n">
         <v>19</v>
@@ -1357,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
         <v>10</v>
@@ -1500,7 +1567,7 @@
         <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1524,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
         <v>18</v>
@@ -1536,7 +1603,7 @@
         <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1661,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2040,13 +2107,13 @@
         <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN9" t="n">
         <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
         <v>17</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2082,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>0.591</v>
+        <v>0.581</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="J10" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
         <v>9.800000000000001</v>
@@ -2147,55 +2214,55 @@
         <v>27.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O10" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="R10" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T10" t="n">
         <v>42.2</v>
       </c>
       <c r="U10" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V10" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AA10" t="n">
         <v>22.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>109.3</v>
+        <v>109</v>
       </c>
       <c r="AC10" t="n">
         <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>9</v>
@@ -2228,16 +2295,16 @@
         <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
         <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>19</v>
@@ -2255,10 +2322,10 @@
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -2413,7 +2480,7 @@
         <v>27</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ11" t="n">
         <v>22</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.432</v>
+        <v>0.442</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J12" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.443</v>
@@ -2508,67 +2575,67 @@
         <v>8.6</v>
       </c>
       <c r="M12" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O12" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.759</v>
+        <v>0.755</v>
       </c>
       <c r="R12" t="n">
         <v>11.7</v>
       </c>
       <c r="S12" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T12" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AA12" t="n">
         <v>22</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.3</v>
+        <v>103.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>17</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
@@ -2595,13 +2662,13 @@
         <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>
@@ -2616,10 +2683,10 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>23</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2814,7 @@
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2789,10 +2856,10 @@
         <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -2813,7 +2880,7 @@
         <v>13</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>5.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2959,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
@@ -2974,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>23</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
         <v>9</v>
@@ -3138,13 +3205,13 @@
         <v>6</v>
       </c>
       <c r="AO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
@@ -3153,7 +3220,7 @@
         <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>21</v>
@@ -3174,7 +3241,7 @@
         <v>3</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J16" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O16" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.703</v>
+        <v>0.706</v>
       </c>
       <c r="R16" t="n">
         <v>9.5</v>
@@ -3260,46 +3327,46 @@
         <v>38.6</v>
       </c>
       <c r="U16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
         <v>7.3</v>
       </c>
       <c r="X16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y16" t="n">
         <v>3.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA16" t="n">
         <v>22</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG16" t="n">
         <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3320,13 +3387,13 @@
         <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3341,13 +3408,13 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>2</v>
@@ -3356,10 +3423,10 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -3391,22 +3458,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.395</v>
+        <v>0.381</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J17" t="n">
         <v>80.5</v>
@@ -3415,46 +3482,46 @@
         <v>0.452</v>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="M17" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
         <v>17</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.746</v>
       </c>
       <c r="R17" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T17" t="n">
         <v>40.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W17" t="n">
         <v>6.8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z17" t="n">
         <v>21.8</v>
@@ -3463,16 +3530,16 @@
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF17" t="n">
         <v>23</v>
@@ -3481,7 +3548,7 @@
         <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
@@ -3493,13 +3560,13 @@
         <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
@@ -3508,10 +3575,10 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3520,10 +3587,10 @@
         <v>26</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
@@ -3532,7 +3599,7 @@
         <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ17" t="n">
         <v>21</v>
@@ -3541,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-8.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG18" t="n">
         <v>30</v>
@@ -3675,10 +3742,10 @@
         <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -3755,58 +3822,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>0.429</v>
+        <v>0.439</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="J19" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
         <v>17</v>
       </c>
       <c r="N19" t="n">
-        <v>0.328</v>
+        <v>0.326</v>
       </c>
       <c r="O19" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="P19" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R19" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T19" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="V19" t="n">
         <v>15.7</v>
@@ -3815,37 +3882,37 @@
         <v>6.7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z19" t="n">
         <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>94</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.1</v>
+        <v>-6.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG19" t="n">
         <v>19</v>
       </c>
-      <c r="AG19" t="n">
-        <v>20</v>
-      </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3857,7 +3924,7 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
@@ -3869,25 +3936,25 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>25</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3896,7 +3963,7 @@
         <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3905,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4075,10 +4142,10 @@
         <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4090,7 +4157,7 @@
         <v>13</v>
       </c>
       <c r="BC20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4245,7 +4312,7 @@
         <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF22" t="n">
         <v>9</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF23" t="n">
         <v>25</v>
@@ -4615,7 +4682,7 @@
         <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
@@ -4624,7 +4691,7 @@
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
         <v>9</v>
@@ -4633,7 +4700,7 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4773,7 +4840,7 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO24" t="n">
         <v>24</v>
@@ -4800,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5116,7 +5183,7 @@
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
@@ -5229,7 +5296,7 @@
         <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.459</v>
@@ -5238,28 +5305,28 @@
         <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.384</v>
+        <v>0.389</v>
       </c>
       <c r="O27" t="n">
         <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S27" t="n">
         <v>31.3</v>
       </c>
       <c r="T27" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U27" t="n">
         <v>21.9</v>
@@ -5274,34 +5341,34 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z27" t="n">
         <v>18.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>18</v>
@@ -5319,16 +5386,16 @@
         <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR27" t="n">
         <v>22</v>
@@ -5337,7 +5404,7 @@
         <v>13</v>
       </c>
       <c r="AT27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU27" t="n">
         <v>11</v>
@@ -5358,13 +5425,13 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
         <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5483,7 +5550,7 @@
         <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5501,7 +5568,7 @@
         <v>27</v>
       </c>
       <c r="AN28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO28" t="n">
         <v>23</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5531,10 +5598,10 @@
         <v>26</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5665,7 +5732,7 @@
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5716,7 +5783,7 @@
         <v>25</v>
       </c>
       <c r="AY29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
@@ -5874,10 +5941,10 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6053,13 +6120,13 @@
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
         <v>16</v>
@@ -6080,7 +6147,7 @@
         <v>12</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-24-2007-08</t>
+          <t>2008-01-24</t>
         </is>
       </c>
     </row>
